--- a/Assets/Scripts/StorySystemPackage/ScriptableObjects/animalclaw.xlsx
+++ b/Assets/Scripts/StorySystemPackage/ScriptableObjects/animalclaw.xlsx
@@ -983,7 +983,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="90" customWidth="1"/>
@@ -1230,6 +1230,72 @@
         <v>39</v>
       </c>
     </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Oh no! That's not the correct animal! Listen to the sound again!</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Encouraging</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>animalclaw</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>wronganimal1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Oops! That's not the right one! Let's listen to the sound again!</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Encouraging</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>animalclaw</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>wronganimal2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Uh-oh! That's not the animal! Press the sound button and listen again!</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Encouraging</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>animalclaw</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>wronganimal3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
